--- a/ecom.bitm.swagLabs/src/test/resources/SauceDemo_TestData.xlsx
+++ b/ecom.bitm.swagLabs/src/test/resources/SauceDemo_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E786A26F-1D56-430E-A0A7-7910BA3EFFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{EE5D844F-0C56-4CD6-BF85-3FAC24E81A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>shaik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saniya </t>
   </si>
 </sst>
 </file>
@@ -562,6 +565,15 @@
       <c r="D6" t="s">
         <v>10</v>
       </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>583101</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
